--- a/mysite/samples/example-library-import.xlsx
+++ b/mysite/samples/example-library-import.xlsx
@@ -100,7 +100,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the “art” of taking life as apprentice Scythes.</t>
+          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the "art" of taking life as apprentice Scythes.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the “art” of taking life as apprentice Scythes.</t>
+          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the "art" of taking life as apprentice Scythes.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -170,7 +170,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the “art” of taking life as apprentice Scythes.</t>
+          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the "art" of taking life as apprentice Scythes.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -275,7 +275,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the “art” of taking life as apprentice Scythes.</t>
+          <t xml:space="preserve">In a world where disease, war and crime have been eliminated, two teens must master the "art" of taking life as apprentice Scythes.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -375,6 +375,60 @@
         <is>
           <t xml:space="preserve">https://covers.openlibrary.org/b/id/8479577-M.jpg</t>
         </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2054</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neal Shusterman</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>9781442472426</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Numeric title AND numeric ISBN, both stored as number cells.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Available</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scythe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neal Shusterman</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>61097314</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ISBN-10 stored as a number — leading zero stripped by the exporter.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Available</t>
+        </is>
+      </c>
+      <c r="H12">
+        <v>45000</v>
       </c>
     </row>
   </sheetData>
